--- a/artfynd/A 23829-2023 artfynd.xlsx
+++ b/artfynd/A 23829-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 23829-2023 artfynd.xlsx
+++ b/artfynd/A 23829-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>96486470</v>
+        <v>106822090</v>
       </c>
       <c r="B2" t="n">
-        <v>90674</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91930</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5964</v>
+        <v>5442</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Nykoxet, NV om, Srm</t>
+          <t>Bornjöns Naturreservat, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>657800.4369817743</v>
+        <v>657739</v>
       </c>
       <c r="R2" t="n">
-        <v>6571241.96882416</v>
+        <v>6571170</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2021-10-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Flera fruktkroppar i äldre barrblandskog.</t>
+          <t>2022-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,22 +754,249 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Amelie Lindhagen</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Amelie Lindhagen, David Falk</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Bornsjön</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>96486470</v>
+      </c>
+      <c r="B3" t="n">
+        <v>93233</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Nykoxet, NV om, Srm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>657800</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6571242</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2021-10-04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Flera fruktkroppar i äldre barrblandskog.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Bo Törnquist</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Bo Törnquist</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>86276108</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Botkyrka, Srm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>657540</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6571287</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Botkyrka</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-06-15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-06-15</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23829-2023 artfynd.xlsx
+++ b/artfynd/A 23829-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -771,6 +776,11 @@
       <c r="AY2" t="inlineStr">
         <is>
           <t>Bornsjön</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106822090</t>
         </is>
       </c>
     </row>
@@ -879,6 +889,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96486470</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -997,8 +1012,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/86276108</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>